--- a/sample/견적서양식_sample.xlsx
+++ b/sample/견적서양식_sample.xlsx
@@ -1333,11 +1333,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFECE9D8"/>
   </sheetPr>
-  <dimension ref="A1:AP36"/>
+  <dimension ref="A1:AP42"/>
   <sheetFormatPr defaultColWidth="1.77734375" defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.77734375" style="4" customWidth="1"/>
@@ -2639,233 +2639,496 @@
       <c r="AO31" s="57"/>
       <c r="AP31" s="58"/>
     </row>
-    <row r="32" spans="1:42" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="65" t="s">
+    <row r="32" spans="1:42" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="38"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="57"/>
+      <c r="S32" s="57"/>
+      <c r="T32" s="57"/>
+      <c r="U32" s="57"/>
+      <c r="V32" s="57"/>
+      <c r="W32" s="57"/>
+      <c r="X32" s="57"/>
+      <c r="Y32" s="57"/>
+      <c r="Z32" s="57"/>
+      <c r="AA32" s="57"/>
+      <c r="AB32" s="57"/>
+      <c r="AC32" s="57"/>
+      <c r="AD32" s="57"/>
+      <c r="AE32" s="57"/>
+      <c r="AF32" s="57"/>
+      <c r="AG32" s="57"/>
+      <c r="AH32" s="57"/>
+      <c r="AI32" s="57"/>
+      <c r="AJ32" s="57"/>
+      <c r="AK32" s="57"/>
+      <c r="AL32" s="57"/>
+      <c r="AM32" s="57"/>
+      <c r="AN32" s="57"/>
+      <c r="AO32" s="57"/>
+      <c r="AP32" s="58"/>
+    </row>
+    <row r="33" spans="1:42" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="38"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="57"/>
+      <c r="S33" s="57"/>
+      <c r="T33" s="57"/>
+      <c r="U33" s="57"/>
+      <c r="V33" s="57"/>
+      <c r="W33" s="57"/>
+      <c r="X33" s="57"/>
+      <c r="Y33" s="57"/>
+      <c r="Z33" s="57"/>
+      <c r="AA33" s="57"/>
+      <c r="AB33" s="57"/>
+      <c r="AC33" s="57"/>
+      <c r="AD33" s="57"/>
+      <c r="AE33" s="57"/>
+      <c r="AF33" s="57"/>
+      <c r="AG33" s="57"/>
+      <c r="AH33" s="57"/>
+      <c r="AI33" s="57"/>
+      <c r="AJ33" s="57"/>
+      <c r="AK33" s="57"/>
+      <c r="AL33" s="57"/>
+      <c r="AM33" s="57"/>
+      <c r="AN33" s="57"/>
+      <c r="AO33" s="57"/>
+      <c r="AP33" s="58"/>
+    </row>
+    <row r="34" spans="1:42" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="38"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="57"/>
+      <c r="S34" s="57"/>
+      <c r="T34" s="57"/>
+      <c r="U34" s="57"/>
+      <c r="V34" s="57"/>
+      <c r="W34" s="57"/>
+      <c r="X34" s="57"/>
+      <c r="Y34" s="57"/>
+      <c r="Z34" s="57"/>
+      <c r="AA34" s="57"/>
+      <c r="AB34" s="57"/>
+      <c r="AC34" s="57"/>
+      <c r="AD34" s="57"/>
+      <c r="AE34" s="57"/>
+      <c r="AF34" s="57"/>
+      <c r="AG34" s="57"/>
+      <c r="AH34" s="57"/>
+      <c r="AI34" s="57"/>
+      <c r="AJ34" s="57"/>
+      <c r="AK34" s="57"/>
+      <c r="AL34" s="57"/>
+      <c r="AM34" s="57"/>
+      <c r="AN34" s="57"/>
+      <c r="AO34" s="57"/>
+      <c r="AP34" s="58"/>
+    </row>
+    <row r="35" spans="1:42" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="38"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="57"/>
+      <c r="V35" s="57"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="57"/>
+      <c r="Y35" s="57"/>
+      <c r="Z35" s="57"/>
+      <c r="AA35" s="57"/>
+      <c r="AB35" s="57"/>
+      <c r="AC35" s="57"/>
+      <c r="AD35" s="57"/>
+      <c r="AE35" s="57"/>
+      <c r="AF35" s="57"/>
+      <c r="AG35" s="57"/>
+      <c r="AH35" s="57"/>
+      <c r="AI35" s="57"/>
+      <c r="AJ35" s="57"/>
+      <c r="AK35" s="57"/>
+      <c r="AL35" s="57"/>
+      <c r="AM35" s="57"/>
+      <c r="AN35" s="57"/>
+      <c r="AO35" s="57"/>
+      <c r="AP35" s="58"/>
+    </row>
+    <row r="36" spans="1:42" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="38"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="57"/>
+      <c r="V36" s="57"/>
+      <c r="W36" s="57"/>
+      <c r="X36" s="57"/>
+      <c r="Y36" s="57"/>
+      <c r="Z36" s="57"/>
+      <c r="AA36" s="57"/>
+      <c r="AB36" s="57"/>
+      <c r="AC36" s="57"/>
+      <c r="AD36" s="57"/>
+      <c r="AE36" s="57"/>
+      <c r="AF36" s="57"/>
+      <c r="AG36" s="57"/>
+      <c r="AH36" s="57"/>
+      <c r="AI36" s="57"/>
+      <c r="AJ36" s="57"/>
+      <c r="AK36" s="57"/>
+      <c r="AL36" s="57"/>
+      <c r="AM36" s="57"/>
+      <c r="AN36" s="57"/>
+      <c r="AO36" s="57"/>
+      <c r="AP36" s="58"/>
+    </row>
+    <row r="37" spans="1:42" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="38"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="33"/>
+      <c r="N37" s="33"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="57"/>
+      <c r="W37" s="57"/>
+      <c r="X37" s="57"/>
+      <c r="Y37" s="57"/>
+      <c r="Z37" s="57"/>
+      <c r="AA37" s="57"/>
+      <c r="AB37" s="57"/>
+      <c r="AC37" s="57"/>
+      <c r="AD37" s="57"/>
+      <c r="AE37" s="57"/>
+      <c r="AF37" s="57"/>
+      <c r="AG37" s="57"/>
+      <c r="AH37" s="57"/>
+      <c r="AI37" s="57"/>
+      <c r="AJ37" s="57"/>
+      <c r="AK37" s="57"/>
+      <c r="AL37" s="57"/>
+      <c r="AM37" s="57"/>
+      <c r="AN37" s="57"/>
+      <c r="AO37" s="57"/>
+      <c r="AP37" s="58"/>
+    </row>
+    <row r="38" spans="1:42" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="66"/>
-      <c r="C32" s="66"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="66"/>
-      <c r="F32" s="66"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="66"/>
-      <c r="J32" s="66"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="66"/>
-      <c r="M32" s="66"/>
-      <c r="N32" s="66"/>
-      <c r="O32" s="66"/>
-      <c r="P32" s="66"/>
-      <c r="Q32" s="66"/>
-      <c r="R32" s="66"/>
-      <c r="S32" s="66"/>
-      <c r="T32" s="66"/>
-      <c r="U32" s="66"/>
-      <c r="V32" s="66"/>
-      <c r="W32" s="67"/>
-      <c r="X32" s="59"/>
-      <c r="Y32" s="60"/>
-      <c r="Z32" s="60"/>
-      <c r="AA32" s="60"/>
-      <c r="AB32" s="60"/>
-      <c r="AC32" s="60"/>
-      <c r="AD32" s="60"/>
-      <c r="AE32" s="60"/>
-      <c r="AF32" s="60"/>
-      <c r="AG32" s="63"/>
-      <c r="AH32" s="59"/>
-      <c r="AI32" s="60"/>
-      <c r="AJ32" s="60"/>
-      <c r="AK32" s="61"/>
-      <c r="AL32" s="62"/>
-      <c r="AM32" s="60"/>
-      <c r="AN32" s="60"/>
-      <c r="AO32" s="60"/>
-      <c r="AP32" s="63"/>
-    </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="A33" s="5"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="64"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
-      <c r="L33" s="64"/>
-      <c r="M33" s="64"/>
-      <c r="N33" s="64"/>
-      <c r="O33" s="64"/>
-      <c r="P33" s="64"/>
-      <c r="Q33" s="64"/>
-      <c r="R33" s="64"/>
-      <c r="S33" s="64"/>
-      <c r="T33" s="64"/>
-      <c r="U33" s="64"/>
-      <c r="V33" s="64"/>
-      <c r="W33" s="64"/>
-      <c r="X33" s="64"/>
-      <c r="Y33" s="64"/>
-      <c r="Z33" s="64"/>
-      <c r="AA33" s="64"/>
-      <c r="AB33" s="64"/>
-      <c r="AC33" s="64"/>
-      <c r="AD33" s="64"/>
-      <c r="AE33" s="64"/>
-      <c r="AF33" s="64"/>
-      <c r="AG33" s="64"/>
-      <c r="AH33" s="64"/>
-      <c r="AI33" s="64"/>
-      <c r="AJ33" s="64"/>
-      <c r="AK33" s="64"/>
-      <c r="AL33" s="64"/>
-      <c r="AM33" s="64"/>
-      <c r="AN33" s="64"/>
-      <c r="AO33" s="64"/>
-      <c r="AP33" s="6"/>
-    </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="A34" s="5"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="64"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="64"/>
-      <c r="F34" s="64"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="64"/>
-      <c r="K34" s="64"/>
-      <c r="L34" s="64"/>
-      <c r="M34" s="64"/>
-      <c r="N34" s="64"/>
-      <c r="O34" s="64"/>
-      <c r="P34" s="64"/>
-      <c r="Q34" s="64"/>
-      <c r="R34" s="64"/>
-      <c r="S34" s="64"/>
-      <c r="T34" s="64"/>
-      <c r="U34" s="64"/>
-      <c r="V34" s="64"/>
-      <c r="W34" s="64"/>
-      <c r="X34" s="64"/>
-      <c r="Y34" s="64"/>
-      <c r="Z34" s="64"/>
-      <c r="AA34" s="64"/>
-      <c r="AB34" s="64"/>
-      <c r="AC34" s="64"/>
-      <c r="AD34" s="64"/>
-      <c r="AE34" s="64"/>
-      <c r="AF34" s="64"/>
-      <c r="AG34" s="64"/>
-      <c r="AH34" s="64"/>
-      <c r="AI34" s="64"/>
-      <c r="AJ34" s="64"/>
-      <c r="AK34" s="64"/>
-      <c r="AL34" s="64"/>
-      <c r="AM34" s="64"/>
-      <c r="AN34" s="64"/>
-      <c r="AO34" s="64"/>
-      <c r="AP34" s="6"/>
-    </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.15">
-      <c r="A35" s="5"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="64"/>
-      <c r="K35" s="64"/>
-      <c r="L35" s="64"/>
-      <c r="M35" s="64"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="64"/>
-      <c r="P35" s="64"/>
-      <c r="Q35" s="64"/>
-      <c r="R35" s="64"/>
-      <c r="S35" s="64"/>
-      <c r="T35" s="64"/>
-      <c r="U35" s="64"/>
-      <c r="V35" s="64"/>
-      <c r="W35" s="64"/>
-      <c r="X35" s="64"/>
-      <c r="Y35" s="64"/>
-      <c r="Z35" s="64"/>
-      <c r="AA35" s="64"/>
-      <c r="AB35" s="64"/>
-      <c r="AC35" s="64"/>
-      <c r="AD35" s="64"/>
-      <c r="AE35" s="64"/>
-      <c r="AF35" s="64"/>
-      <c r="AG35" s="64"/>
-      <c r="AH35" s="64"/>
-      <c r="AI35" s="64"/>
-      <c r="AJ35" s="64"/>
-      <c r="AK35" s="64"/>
-      <c r="AL35" s="64"/>
-      <c r="AM35" s="64"/>
-      <c r="AN35" s="64"/>
-      <c r="AO35" s="64"/>
-      <c r="AP35" s="6"/>
-    </row>
-    <row r="36" spans="1:42" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="51" t="s">
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="66"/>
+      <c r="K38" s="66"/>
+      <c r="L38" s="66"/>
+      <c r="M38" s="66"/>
+      <c r="N38" s="66"/>
+      <c r="O38" s="66"/>
+      <c r="P38" s="66"/>
+      <c r="Q38" s="66"/>
+      <c r="R38" s="66"/>
+      <c r="S38" s="66"/>
+      <c r="T38" s="66"/>
+      <c r="U38" s="66"/>
+      <c r="V38" s="66"/>
+      <c r="W38" s="67"/>
+      <c r="X38" s="59"/>
+      <c r="Y38" s="60"/>
+      <c r="Z38" s="60"/>
+      <c r="AA38" s="60"/>
+      <c r="AB38" s="60"/>
+      <c r="AC38" s="60"/>
+      <c r="AD38" s="60"/>
+      <c r="AE38" s="60"/>
+      <c r="AF38" s="60"/>
+      <c r="AG38" s="63"/>
+      <c r="AH38" s="59"/>
+      <c r="AI38" s="60"/>
+      <c r="AJ38" s="60"/>
+      <c r="AK38" s="61"/>
+      <c r="AL38" s="62"/>
+      <c r="AM38" s="60"/>
+      <c r="AN38" s="60"/>
+      <c r="AO38" s="60"/>
+      <c r="AP38" s="63"/>
+    </row>
+    <row r="39" spans="1:42" x14ac:dyDescent="0.15">
+      <c r="A39" s="5"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="64"/>
+      <c r="J39" s="64"/>
+      <c r="K39" s="64"/>
+      <c r="L39" s="64"/>
+      <c r="M39" s="64"/>
+      <c r="N39" s="64"/>
+      <c r="O39" s="64"/>
+      <c r="P39" s="64"/>
+      <c r="Q39" s="64"/>
+      <c r="R39" s="64"/>
+      <c r="S39" s="64"/>
+      <c r="T39" s="64"/>
+      <c r="U39" s="64"/>
+      <c r="V39" s="64"/>
+      <c r="W39" s="64"/>
+      <c r="X39" s="64"/>
+      <c r="Y39" s="64"/>
+      <c r="Z39" s="64"/>
+      <c r="AA39" s="64"/>
+      <c r="AB39" s="64"/>
+      <c r="AC39" s="64"/>
+      <c r="AD39" s="64"/>
+      <c r="AE39" s="64"/>
+      <c r="AF39" s="64"/>
+      <c r="AG39" s="64"/>
+      <c r="AH39" s="64"/>
+      <c r="AI39" s="64"/>
+      <c r="AJ39" s="64"/>
+      <c r="AK39" s="64"/>
+      <c r="AL39" s="64"/>
+      <c r="AM39" s="64"/>
+      <c r="AN39" s="64"/>
+      <c r="AO39" s="64"/>
+      <c r="AP39" s="6"/>
+    </row>
+    <row r="40" spans="1:42" x14ac:dyDescent="0.15">
+      <c r="A40" s="5"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="64"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="64"/>
+      <c r="M40" s="64"/>
+      <c r="N40" s="64"/>
+      <c r="O40" s="64"/>
+      <c r="P40" s="64"/>
+      <c r="Q40" s="64"/>
+      <c r="R40" s="64"/>
+      <c r="S40" s="64"/>
+      <c r="T40" s="64"/>
+      <c r="U40" s="64"/>
+      <c r="V40" s="64"/>
+      <c r="W40" s="64"/>
+      <c r="X40" s="64"/>
+      <c r="Y40" s="64"/>
+      <c r="Z40" s="64"/>
+      <c r="AA40" s="64"/>
+      <c r="AB40" s="64"/>
+      <c r="AC40" s="64"/>
+      <c r="AD40" s="64"/>
+      <c r="AE40" s="64"/>
+      <c r="AF40" s="64"/>
+      <c r="AG40" s="64"/>
+      <c r="AH40" s="64"/>
+      <c r="AI40" s="64"/>
+      <c r="AJ40" s="64"/>
+      <c r="AK40" s="64"/>
+      <c r="AL40" s="64"/>
+      <c r="AM40" s="64"/>
+      <c r="AN40" s="64"/>
+      <c r="AO40" s="64"/>
+      <c r="AP40" s="6"/>
+    </row>
+    <row r="41" spans="1:42" x14ac:dyDescent="0.15">
+      <c r="A41" s="5"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="64"/>
+      <c r="J41" s="64"/>
+      <c r="K41" s="64"/>
+      <c r="L41" s="64"/>
+      <c r="M41" s="64"/>
+      <c r="N41" s="64"/>
+      <c r="O41" s="64"/>
+      <c r="P41" s="64"/>
+      <c r="Q41" s="64"/>
+      <c r="R41" s="64"/>
+      <c r="S41" s="64"/>
+      <c r="T41" s="64"/>
+      <c r="U41" s="64"/>
+      <c r="V41" s="64"/>
+      <c r="W41" s="64"/>
+      <c r="X41" s="64"/>
+      <c r="Y41" s="64"/>
+      <c r="Z41" s="64"/>
+      <c r="AA41" s="64"/>
+      <c r="AB41" s="64"/>
+      <c r="AC41" s="64"/>
+      <c r="AD41" s="64"/>
+      <c r="AE41" s="64"/>
+      <c r="AF41" s="64"/>
+      <c r="AG41" s="64"/>
+      <c r="AH41" s="64"/>
+      <c r="AI41" s="64"/>
+      <c r="AJ41" s="64"/>
+      <c r="AK41" s="64"/>
+      <c r="AL41" s="64"/>
+      <c r="AM41" s="64"/>
+      <c r="AN41" s="64"/>
+      <c r="AO41" s="64"/>
+      <c r="AP41" s="6"/>
+    </row>
+    <row r="42" spans="1:42" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="52"/>
-      <c r="Q36" s="52"/>
-      <c r="R36" s="52"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="52"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="52"/>
-      <c r="W36" s="52"/>
-      <c r="X36" s="52"/>
-      <c r="Y36" s="52"/>
-      <c r="Z36" s="52"/>
-      <c r="AA36" s="52"/>
-      <c r="AB36" s="52"/>
-      <c r="AC36" s="52"/>
-      <c r="AD36" s="52"/>
-      <c r="AE36" s="52"/>
-      <c r="AF36" s="52"/>
-      <c r="AG36" s="52"/>
-      <c r="AH36" s="52"/>
-      <c r="AI36" s="52"/>
-      <c r="AJ36" s="52"/>
-      <c r="AK36" s="52"/>
-      <c r="AL36" s="52"/>
-      <c r="AM36" s="52"/>
-      <c r="AN36" s="52"/>
-      <c r="AO36" s="52"/>
-      <c r="AP36" s="53"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="52"/>
+      <c r="O42" s="52"/>
+      <c r="P42" s="52"/>
+      <c r="Q42" s="52"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="52"/>
+      <c r="T42" s="52"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="52"/>
+      <c r="W42" s="52"/>
+      <c r="X42" s="52"/>
+      <c r="Y42" s="52"/>
+      <c r="Z42" s="52"/>
+      <c r="AA42" s="52"/>
+      <c r="AB42" s="52"/>
+      <c r="AC42" s="52"/>
+      <c r="AD42" s="52"/>
+      <c r="AE42" s="52"/>
+      <c r="AF42" s="52"/>
+      <c r="AG42" s="52"/>
+      <c r="AH42" s="52"/>
+      <c r="AI42" s="52"/>
+      <c r="AJ42" s="52"/>
+      <c r="AK42" s="52"/>
+      <c r="AL42" s="52"/>
+      <c r="AM42" s="52"/>
+      <c r="AN42" s="52"/>
+      <c r="AO42" s="52"/>
+      <c r="AP42" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="170">
-    <mergeCell ref="A36:AP36"/>
+  <mergeCells count="215">
     <mergeCell ref="AL30:AP30"/>
     <mergeCell ref="AH31:AK31"/>
     <mergeCell ref="AL31:AP31"/>
@@ -2989,13 +3252,6 @@
     <mergeCell ref="K31:N31"/>
     <mergeCell ref="O31:Q31"/>
     <mergeCell ref="R31:W31"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="O32:Q32"/>
-    <mergeCell ref="R32:W32"/>
-    <mergeCell ref="X32:AG32"/>
-    <mergeCell ref="AH32:AK32"/>
-    <mergeCell ref="AL32:AP32"/>
     <mergeCell ref="X26:AG26"/>
     <mergeCell ref="X27:AG27"/>
     <mergeCell ref="X28:AG28"/>
@@ -3035,6 +3291,59 @@
     <mergeCell ref="K20:N20"/>
     <mergeCell ref="O20:Q20"/>
     <mergeCell ref="AL19:AP19"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="R32:W32"/>
+    <mergeCell ref="X32:AG32"/>
+    <mergeCell ref="AH32:AK32"/>
+    <mergeCell ref="AL32:AP32"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="R33:W33"/>
+    <mergeCell ref="X33:AG33"/>
+    <mergeCell ref="AH33:AK33"/>
+    <mergeCell ref="AL33:AP33"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="R34:W34"/>
+    <mergeCell ref="X34:AG34"/>
+    <mergeCell ref="AH34:AK34"/>
+    <mergeCell ref="AL34:AP34"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="R35:W35"/>
+    <mergeCell ref="X35:AG35"/>
+    <mergeCell ref="AH35:AK35"/>
+    <mergeCell ref="AL35:AP35"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="R36:W36"/>
+    <mergeCell ref="X36:AG36"/>
+    <mergeCell ref="AH36:AK36"/>
+    <mergeCell ref="AL36:AP36"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R37:W37"/>
+    <mergeCell ref="X37:AG37"/>
+    <mergeCell ref="AH37:AK37"/>
+    <mergeCell ref="AL37:AP37"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="O38:Q38"/>
+    <mergeCell ref="R38:W38"/>
+    <mergeCell ref="X38:AG38"/>
+    <mergeCell ref="AH38:AK38"/>
+    <mergeCell ref="AL38:AP38"/>
+    <mergeCell ref="A39:AP39"/>
+    <mergeCell ref="A40:AP40"/>
+    <mergeCell ref="A41:AP41"/>
+    <mergeCell ref="A42:AP42"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/sample/견적서양식_sample.xlsx
+++ b/sample/견적서양식_sample.xlsx
@@ -1333,15 +1333,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FFECE9D8"/>
   </sheetPr>
   <dimension ref="A1:AP42"/>
   <sheetFormatPr defaultColWidth="1.77734375" defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.77734375" style="4" customWidth="1"/>
-    <col min="2" max="16384" width="1.77734375" style="4"/>
+    <col min="1" max="10" width="1.77734375" style="4" customWidth="1"/>
+    <col min="11" max="14" width="2.8" style="4" customWidth="1"/>
+    <col min="15" max="17" width="1.77734375" style="4"/>
+    <col min="18" max="23" width="2.3" style="4" customWidth="1"/>
+    <col min="24" max="32" width="1.4" style="4" customWidth="1"/>
+    <col min="33" max="37" width="2.8" style="4" customWidth="1"/>
+    <col min="38" max="42" width="2.7" style="4" customWidth="1"/>
+    <col min="43" max="16384" width="1.77734375" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15">
